--- a/docs/test-cases-functional.xlsx
+++ b/docs/test-cases-functional.xlsx
@@ -1,46 +1,183 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Функциональные тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Функциональные тест-кейсы" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Приоритет</t>
+  </si>
+  <si>
+    <t>Предусловия</t>
+  </si>
+  <si>
+    <t>Шаги</t>
+  </si>
+  <si>
+    <t>Ожидаемый результат</t>
+  </si>
+  <si>
+    <t>TC-01</t>
+  </si>
+  <si>
+    <t>Вход в систему с корректными данными</t>
+  </si>
+  <si>
+    <t>Высокий</t>
+  </si>
+  <si>
+    <t>Открыта страница входа, известны корректные логин и пароль</t>
+  </si>
+  <si>
+    <t>1. Открыть сайт yougile.com
+2. Ввести корректный логин в поле «E-mail»
+3. Ввести корректный пароль в поле «Пароль»
+4. Нажать кнопку «Войти»</t>
+  </si>
+  <si>
+    <t>Открывается рабочее пространство (дашборд проектов), пользователь авторизован</t>
+  </si>
+  <si>
+    <t>TC-02</t>
+  </si>
+  <si>
+    <t>Создание проекта</t>
+  </si>
+  <si>
+    <t>Пользователь авторизован</t>
+  </si>
+  <si>
+    <t>1. На дашборде нажать кнопку создания проекта
+2. Ввести название проекта (уникальное)
+3. При необходимости выбрать участников
+4. Подтвердить создание</t>
+  </si>
+  <si>
+    <t>Проект создан и отображается в списке проектов</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>Редактирование названия проекта</t>
+  </si>
+  <si>
+    <t>Средний</t>
+  </si>
+  <si>
+    <t>Пользователь авторизован, существует созданный проект</t>
+  </si>
+  <si>
+    <t>1. Открыть карточку проекта
+2. Нажать на название проекта
+3. Изменить название
+4. Сохранить изменения</t>
+  </si>
+  <si>
+    <t>Новое название отображается в карточке проекта и в списке проектов</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>Создание задачи на доске</t>
+  </si>
+  <si>
+    <t>Пользователь авторизован, существует проект с доской</t>
+  </si>
+  <si>
+    <t>1. Открыть доску проекта
+2. Нажать кнопку добавления задачи
+3. Ввести название задачи
+4. Подтвердить создание</t>
+  </si>
+  <si>
+    <t>Задача создана и отображается в колонке доски</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>Изменение статуса задачи (перенос по колонкам)</t>
+  </si>
+  <si>
+    <t>Существует задача на доске</t>
+  </si>
+  <si>
+    <t>1. Открыть доску проекта
+2. Перетащить карточку задачи в другую колонку (например, «В работе»)
+3. Дождаться сохранения</t>
+  </si>
+  <si>
+    <t>Задача отображается в новой колонке, статус изменён</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>Добавление комментария к задаче</t>
+  </si>
+  <si>
+    <t>Существует задача</t>
+  </si>
+  <si>
+    <t>1. Открыть карточку задачи
+2. В поле комментария ввести текст
+3. Нажать кнопку отправки</t>
+  </si>
+  <si>
+    <t>Комментарий сохранён и отображается в карточке задачи</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF6C5CE7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,103 +191,35 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -438,263 +507,155 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="6" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Предусловия</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Шаги</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Ожидаемый результат</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Вход в систему с корректными данными</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Открыта страница входа, известны корректные логин и пароль</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1. Открыть сайт yougile.com
-2. Ввести корректный логин в поле «E-mail»
-3. Ввести корректный пароль в поле «Пароль»
-4. Нажать кнопку «Войти»</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Открывается рабочее пространство (дашборд проектов), пользователь авторизован</t>
-        </is>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Создание проекта</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Пользователь авторизован</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1. На дашборде нажать кнопку создания проекта
-2. Ввести название проекта (уникальное)
-3. При необходимости выбрать участников
-4. Подтвердить создание</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Проект создан и отображается в списке проектов</t>
-        </is>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Редактирование названия проекта</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Пользователь авторизован, существует созданный проект</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1. Открыть карточку проекта
-2. Нажать на название проекта
-3. Изменить название
-4. Сохранить изменения</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Новое название отображается в карточке проекта и в списке проектов</t>
-        </is>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Создание задачи на доске</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Пользователь авторизован, существует проект с доской</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1. Открыть доску проекта
-2. Нажать кнопку добавления задачи
-3. Ввести название задачи
-4. Подтвердить создание</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Задача создана и отображается в колонке доски</t>
-        </is>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Изменение статуса задачи (перенос по колонкам)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Существует задача на доске</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1. Открыть доску проекта
-2. Перетащить карточку задачи в другую колонку (например, «В работе»)
-3. Дождаться сохранения</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Задача отображается в новой колонке, статус изменён</t>
-        </is>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Добавление комментария к задаче</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Существует задача</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1. Открыть карточку задачи
-2. В поле комментария ввести текст
-3. Нажать кнопку отправки</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Комментарий сохранён и отображается в карточке задачи</t>
-        </is>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/test-cases-functional.xlsx
+++ b/docs/test-cases-functional.xlsx
@@ -1,183 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Функциональные тест-кейсы" sheetId="1" r:id="rId1"/>
+    <sheet name="Функциональные тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Название</t>
-  </si>
-  <si>
-    <t>Приоритет</t>
-  </si>
-  <si>
-    <t>Предусловия</t>
-  </si>
-  <si>
-    <t>Шаги</t>
-  </si>
-  <si>
-    <t>Ожидаемый результат</t>
-  </si>
-  <si>
-    <t>TC-01</t>
-  </si>
-  <si>
-    <t>Вход в систему с корректными данными</t>
-  </si>
-  <si>
-    <t>Высокий</t>
-  </si>
-  <si>
-    <t>Открыта страница входа, известны корректные логин и пароль</t>
-  </si>
-  <si>
-    <t>1. Открыть сайт yougile.com
-2. Ввести корректный логин в поле «E-mail»
-3. Ввести корректный пароль в поле «Пароль»
-4. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>Открывается рабочее пространство (дашборд проектов), пользователь авторизован</t>
-  </si>
-  <si>
-    <t>TC-02</t>
-  </si>
-  <si>
-    <t>Создание проекта</t>
-  </si>
-  <si>
-    <t>Пользователь авторизован</t>
-  </si>
-  <si>
-    <t>1. На дашборде нажать кнопку создания проекта
-2. Ввести название проекта (уникальное)
-3. При необходимости выбрать участников
-4. Подтвердить создание</t>
-  </si>
-  <si>
-    <t>Проект создан и отображается в списке проектов</t>
-  </si>
-  <si>
-    <t>TC-03</t>
-  </si>
-  <si>
-    <t>Редактирование названия проекта</t>
-  </si>
-  <si>
-    <t>Средний</t>
-  </si>
-  <si>
-    <t>Пользователь авторизован, существует созданный проект</t>
-  </si>
-  <si>
-    <t>1. Открыть карточку проекта
-2. Нажать на название проекта
-3. Изменить название
-4. Сохранить изменения</t>
-  </si>
-  <si>
-    <t>Новое название отображается в карточке проекта и в списке проектов</t>
-  </si>
-  <si>
-    <t>TC-04</t>
-  </si>
-  <si>
-    <t>Создание задачи на доске</t>
-  </si>
-  <si>
-    <t>Пользователь авторизован, существует проект с доской</t>
-  </si>
-  <si>
-    <t>1. Открыть доску проекта
-2. Нажать кнопку добавления задачи
-3. Ввести название задачи
-4. Подтвердить создание</t>
-  </si>
-  <si>
-    <t>Задача создана и отображается в колонке доски</t>
-  </si>
-  <si>
-    <t>TC-05</t>
-  </si>
-  <si>
-    <t>Изменение статуса задачи (перенос по колонкам)</t>
-  </si>
-  <si>
-    <t>Существует задача на доске</t>
-  </si>
-  <si>
-    <t>1. Открыть доску проекта
-2. Перетащить карточку задачи в другую колонку (например, «В работе»)
-3. Дождаться сохранения</t>
-  </si>
-  <si>
-    <t>Задача отображается в новой колонке, статус изменён</t>
-  </si>
-  <si>
-    <t>TC-06</t>
-  </si>
-  <si>
-    <t>Добавление комментария к задаче</t>
-  </si>
-  <si>
-    <t>Существует задача</t>
-  </si>
-  <si>
-    <t>1. Открыть карточку задачи
-2. В поле комментария ввести текст
-3. Нажать кнопку отправки</t>
-  </si>
-  <si>
-    <t>Комментарий сохранён и отображается в карточке задачи</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6C5CE7"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -191,35 +54,103 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -507,155 +438,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="6" width="22.7109375" customWidth="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Предусловия</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Шаги (с ожидаемым результатом каждого шага)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ожидаемый результат</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Вход в систему с корректными данными</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Открыта страница входа, известны корректные логин и пароль</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть сайт yougile.com — ОР: открылась страница входа с полями «E-mail» и «Пароль»
+2. Ввести корректный логин в поле «E-mail» — ОР: введённый логин отображается в поле
+3. Ввести корректный пароль в поле «Пароль» — ОР: пароль введён и скрыт точками
+4. Нажать кнопку «Войти» — ОР: открывается рабочее пространство (дашборд проектов)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь авторизован, открыт дашборд проектов</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Создание проекта</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь авторизован</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1. На дашборде нажать кнопку создания проекта — ОР: открылась форма создания проекта
+2. Ввести название проекта (уникальное) — ОР: название отображается в поле ввода
+3. При необходимости выбрать участников — ОР: участники добавлены в проект
+4. Подтвердить создание — ОР: проект сохранился</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Проект создан и отображается в списке проектов</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>22</v>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Редактирование названия проекта</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь авторизован, существует созданный проект</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть карточку проекта — ОР: открылась карточка проекта с текущим названием
+2. Нажать на название проекта — ОР: название стало доступно для редактирования
+3. Изменить название — ОР: новое название отображается в поле
+4. Сохранить изменения — ОР: изменения сохранились</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Новое название отображается в карточке проекта и в списке проектов</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>27</v>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Создание задачи на доске</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Пользователь авторизован, существует проект с доской</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть доску проекта — ОР: открылась канбан-доска с колонками
+2. Нажать кнопку добавления задачи — ОР: появилась форма ввода названия задачи
+3. Ввести название задачи — ОР: название отображается в поле
+4. Подтвердить создание — ОР: задача появилась в колонке доски</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Задача создана и отображается в колонке доски</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Изменение статуса задачи (перенос по колонкам)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Существует задача на доске</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть доску проекта — ОР: доска с задачей отображается
+2. Перетащить карточку задачи в другую колонку (например, «В работе») — ОР: карточка переместилась в целевую колонку
+3. Дождаться сохранения — ОР: статус задачи обновился в интерфейсе</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Задача отображается в новой колонке, статус изменён</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>37</v>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Добавление комментария к задаче</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Существует задача</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1. Открыть карточку задачи — ОР: карточка задачи с блоком комментариев открылась
+2. В поле комментария ввести текст — ОР: текст отображается в поле ввода
+3. Нажать кнопку отправки — ОР: комментарий появился в блоке комментариев</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Комментарий сохранён и отображается в карточке задачи</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>